--- a/최종체크리스트v2.xlsx
+++ b/최종체크리스트v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\shorts\일본시니어\통합콘텐츠 생성기\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A61A85-1359-4BDB-8BF0-4ACB2316BC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92EA2A6-34D1-4794-BD0C-C36D53CB0767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29775" yWindow="1785" windowWidth="16560" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="✅ 체크리스트" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="196">
   <si>
     <t>🚀  통합콘텐츠 생성기 — 내가 해야 할 것 전체 체크리스트 (판매 완료까지)</t>
   </si>
@@ -56,93 +56,19 @@
     <t>🔴 긴급수정</t>
   </si>
   <si>
-    <t>index.html 메인화면 정리
-(카테고리 카드만 보이게)</t>
-  </si>
-  <si>
-    <t>index.html 메인화면을 정리해줘.
-일반탭에는 카테고리 사이드바+카드만 보여야 해.
-가이드/어린이 내용이 메인에 섞인 것 제거.
-탭별 완전 분리:
-- 일반탭: 카테고리 카드
-- 어린이탭: 어린이 모드
-- 가이드탭: 가이드
-- 설정탭: 설정</t>
-  </si>
-  <si>
-    <t>브라우저에서 index.html 열고
-카테고리 카드만 깔끔하게
-보이면 성공</t>
-  </si>
-  <si>
     <t>⬜ 미완료</t>
   </si>
   <si>
-    <t>🔴 긴급</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>engines/content/index.html
-파일 생성 (없음)</t>
-  </si>
-  <si>
-    <t>engines/content/index.html 만들어줘.
-콘텐츠 유형 카드: 블로그/뉴스레터/전자책/웹툰/SNS
-공통입력: 주제/대상독자/톤/길이
-유형선택시 세부옵션 자동변경
-AI생성버튼/복사저장버튼
-한국어+일본어 동시생성
-core/api-adapter.js 연결
-상단 ← 허브 버튼</t>
-  </si>
-  <si>
-    <t>파일 더블클릭 →
-콘텐츠 유형 카드 보이면 성공</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
-    <t>대본 카드 클릭 시
-해당 탭만 단독으로 열리게 수정</t>
-  </si>
-  <si>
-    <t>index.html에서 대본생성기 카드 클릭 시
-전체 대본생성기가 열리는 문제 수정.
-각 카드별 URL 파라미터 연결:
-일반대본→?tab=gen
-통합생성→?tab=batch
-가사음원→?tab=lyric
-감동스토리→?tab=story
-파라미터 있으면 해당탭만 단독표시</t>
-  </si>
-  <si>
-    <t>일반대본 카드 클릭 →
-일반대본만 보이면 성공</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
     <t>⚡ AI연결</t>
-  </si>
-  <si>
-    <t>대본생성기에서
-실제 AI 생성 테스트</t>
-  </si>
-  <si>
-    <t>engines/script/index.html 열고
-API키 입력 후:
-주제: '고양이 재미있는 영상'
-생성버튼 클릭
-→ 결과 안 나오면:
-'대본생성기 API 연결 안 돼. 고쳐줘'</t>
-  </si>
-  <si>
-    <t>한국어+일본어 대본
-동시에 나오면 성공</t>
   </si>
   <si>
     <t>🔴 필수</t>
@@ -1067,9 +993,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1221,6 +1144,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1535,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1558,1031 +1484,945 @@
       <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="54"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="54"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="96" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="8" t="s">
+    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="96" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="8" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="96" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="E8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="F9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>29</v>
+      <c r="F10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="36" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="F12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="B13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="F13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>50</v>
+      <c r="F14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E16" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>29</v>
+      <c r="F16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B18" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E18" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>50</v>
+      <c r="F18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="F19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="B20" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E20" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>50</v>
+      <c r="F20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B22" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E22" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>50</v>
+      <c r="F22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E24" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="F24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+      <c r="B25" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="C25" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E25" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="F25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B26" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E26" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="F26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="B27" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E27" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="F27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="96" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
         <v>105</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
-        <v>110</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="C28" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E30" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="96" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>29</v>
+      <c r="F30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E32" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="F32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+      <c r="B33" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="C33" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E33" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="F33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="96" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B33" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="B34" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E34" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+      <c r="F34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="B35" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E35" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="F35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B36" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E36" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="96" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>29</v>
+      <c r="F36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C37" s="4" t="s">
+      <c r="B38" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E38" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>29</v>
+      <c r="F38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B40" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>29</v>
+      <c r="E40" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" s="4" t="s">
+      <c r="E42" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>29</v>
+      <c r="F42" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="48" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C43" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="E44" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>50</v>
+      <c r="F44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="48" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>189</v>
+        <v>176</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -2603,7 +2443,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="58" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="56"/>
@@ -2611,186 +2451,186 @@
       <c r="E1" s="56"/>
     </row>
     <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="53"/>
+      <c r="B12" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="C12" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="53" t="s">
         <v>195</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>197</v>
-      </c>
-      <c r="E11" s="53" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54" t="s">
-        <v>207</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>197</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
